--- a/frontend/public/formats/hpodsc_format.xlsx
+++ b/frontend/public/formats/hpodsc_format.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\visha\Downloads\reports (9)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJECTS FOLDER\SG ENCON\frontend\public\formats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B10C658-23AE-459E-96D6-AE1A91387EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0DFB33-0718-4D97-8EB2-2BEC494FDC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{DCD54F35-77DD-4088-B4D2-500A40C16E37}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>lsm</t>
   </si>
@@ -69,259 +69,28 @@
     <t>integration_state</t>
   </si>
   <si>
-    <t>band_2300</t>
-  </si>
-  <si>
-    <t>band_1800</t>
-  </si>
-  <si>
-    <t>band_850</t>
-  </si>
-  <si>
-    <t>cnum_count_2300</t>
-  </si>
-  <si>
-    <t>total_outage_2300</t>
-  </si>
-  <si>
-    <t>cnum_count_1800</t>
-  </si>
-  <si>
-    <t>total_outage_1800</t>
-  </si>
-  <si>
-    <t>cnum_count_850</t>
-  </si>
-  <si>
-    <t>total_outage_850</t>
-  </si>
-  <si>
     <t>total_cnum_count</t>
   </si>
   <si>
     <t>total_outage</t>
   </si>
   <si>
-    <t>total_availability_2300</t>
-  </si>
-  <si>
-    <t>total_availability_1800</t>
-  </si>
-  <si>
-    <t>total_availability_850</t>
-  </si>
-  <si>
     <t>total_availability</t>
   </si>
   <si>
-    <t>c1_alpa_count_2300</t>
-  </si>
-  <si>
-    <t>c1_beta_count_2300</t>
-  </si>
-  <si>
-    <t>c1_gama_count_2300</t>
-  </si>
-  <si>
-    <t>c1_alpa_outag_2300</t>
-  </si>
-  <si>
-    <t>c1_beta_outag_2300</t>
-  </si>
-  <si>
-    <t>c1_gama_outag_2300</t>
-  </si>
-  <si>
-    <t>c2_alpa_count_2300</t>
-  </si>
-  <si>
-    <t>c2_beta_count_2300</t>
-  </si>
-  <si>
-    <t>c2_gama_count_2300</t>
-  </si>
-  <si>
-    <t>c2_alpa_outag_2300</t>
-  </si>
-  <si>
-    <t>c2_beta_outag_2300</t>
-  </si>
-  <si>
-    <t>c2_gama_outag_2300</t>
-  </si>
-  <si>
-    <t>c1_alpa_count_1800</t>
-  </si>
-  <si>
-    <t>c1_beta_count_1800</t>
-  </si>
-  <si>
-    <t>c1_gama_count_1800</t>
-  </si>
-  <si>
-    <t>c1_alpa_outag_1800</t>
-  </si>
-  <si>
-    <t>c1_beta_outag_1800</t>
-  </si>
-  <si>
-    <t>c1_gama_outag_1800</t>
-  </si>
-  <si>
-    <t>c1_alpa_count_850</t>
-  </si>
-  <si>
-    <t>c1_beta_count_850</t>
-  </si>
-  <si>
-    <t>c1_gama_count_850</t>
-  </si>
-  <si>
-    <t>c1_alpa_outag_850</t>
-  </si>
-  <si>
-    <t>c1_beta_outag_850</t>
-  </si>
-  <si>
-    <t>c1_gama_outag_850</t>
-  </si>
-  <si>
-    <t>c2_alpa_count_850</t>
-  </si>
-  <si>
-    <t>c2_beta_count_850</t>
-  </si>
-  <si>
-    <t>c2_gama_count_850</t>
-  </si>
-  <si>
-    <t>c2_alpa_outag_850</t>
-  </si>
-  <si>
-    <t>c2_beta_outag_850</t>
-  </si>
-  <si>
-    <t>c2_gama_outag_850</t>
-  </si>
-  <si>
-    <t>addn_alpa_count</t>
-  </si>
-  <si>
-    <t>addn_beta_count</t>
-  </si>
-  <si>
-    <t>addn_gama_count</t>
-  </si>
-  <si>
-    <t>addn_alpa_outage</t>
-  </si>
-  <si>
-    <t>addn_beta_outage</t>
-  </si>
-  <si>
-    <t>addn_gama_outage</t>
-  </si>
-  <si>
-    <t>cnum_0_outage</t>
-  </si>
-  <si>
-    <t>cnum_1_outage</t>
-  </si>
-  <si>
-    <t>cnum_2_outage</t>
-  </si>
-  <si>
-    <t>cnum_20_outage</t>
-  </si>
-  <si>
-    <t>cnum_18_outage</t>
-  </si>
-  <si>
-    <t>cnum_19_outage</t>
-  </si>
-  <si>
-    <t>cnum_12_outage</t>
-  </si>
-  <si>
-    <t>cnum_13_outage</t>
-  </si>
-  <si>
-    <t>cnum_14_outage</t>
-  </si>
-  <si>
-    <t>cnum_9_outage</t>
-  </si>
-  <si>
-    <t>cnum_10_outage</t>
-  </si>
-  <si>
-    <t>cnum_11_outage</t>
-  </si>
-  <si>
-    <t>cnum_3_outage</t>
-  </si>
-  <si>
-    <t>cnum_4_outage</t>
-  </si>
-  <si>
-    <t>cnum_5_outage</t>
-  </si>
-  <si>
-    <t>cnum_6_outage</t>
-  </si>
-  <si>
-    <t>cnum_15_outage</t>
-  </si>
-  <si>
-    <t>cnum_24_outage</t>
-  </si>
-  <si>
-    <t>cnum_27_outage</t>
-  </si>
-  <si>
-    <t>cnum_28_outage</t>
-  </si>
-  <si>
-    <t>cnum_29_outage</t>
-  </si>
-  <si>
-    <t>cnum_7_outage</t>
-  </si>
-  <si>
-    <t>cnum_16_outage</t>
-  </si>
-  <si>
-    <t>cnum_25_outage</t>
-  </si>
-  <si>
-    <t>cnum_30_outage</t>
-  </si>
-  <si>
-    <t>cnum_31_outage</t>
-  </si>
-  <si>
-    <t>cnum_32_outage</t>
-  </si>
-  <si>
-    <t>cells_down_gt4hr</t>
-  </si>
-  <si>
-    <t>cells_down_gt4hr_mod</t>
-  </si>
-  <si>
-    <t>aging_band</t>
-  </si>
-  <si>
-    <t>sys_alias</t>
-  </si>
-  <si>
-    <t>ip_addr_1</t>
-  </si>
-  <si>
     <t>cells_up</t>
   </si>
   <si>
-    <t>cells_up_mod</t>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>Punjab</t>
+  </si>
+  <si>
+    <t>Haryana</t>
+  </si>
+  <si>
+    <t>Uttar Pradesh (East)</t>
   </si>
 </sst>
 </file>
@@ -388,7 +157,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -704,10 +473,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52A3340F-DCE3-4BC9-AAE7-F1E138BAF2FF}">
-  <dimension ref="A1:CR1"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:96" ht="113.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -753,248 +522,25 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BQ1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BU1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BV1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BW1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BX1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BY1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="BZ1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CA1" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CB1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="CC1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="CD1" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="CE1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="CF1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="CG1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="CH1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="CI1" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="CJ1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="CK1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="CL1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="CM1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="CN1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="CO1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="CP1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="CQ1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="CR1" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
   </sheetData>
